--- a/proyecto_vivienda_unifamiliar_por_RENZO/cuadro_cargas/cuadro_cargas.xlsx
+++ b/proyecto_vivienda_unifamiliar_por_RENZO/cuadro_cargas/cuadro_cargas.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,28 +26,34 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001E3A8A"/>
+      <color rgb="001B365D"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="004A5568"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,14 +62,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
-        <bgColor rgb="00F3F4F6"/>
+        <fgColor rgb="00F7FAFC"/>
+        <bgColor rgb="00F7FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF8FF"/>
+        <bgColor rgb="00EBF8FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,68 +89,76 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CBD5E0"/>
       </left>
       <right style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CBD5E0"/>
       </right>
       <top style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CBD5E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CBD5E0"/>
       </bottom>
     </border>
     <border>
       <top style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CBD5E0"/>
       </top>
       <bottom style="double">
-        <color rgb="001E3A8A"/>
+        <color rgb="001B365D"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,437 +526,330 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CUADRO DE CARGAS - VIVIENDA UNIFAMILIAR</t>
+          <t>CUADRO DE CARGAS - RESIDENCIAL</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Tablero</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Estudiante: Renzo Gabriel Mamani Galindo  |  Curso: Instalaciones Eléctricas I  |  Universidad: UNAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Circuito</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Descripción (Uso)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Tensión (V)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Fases</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Pot. Inst. (W)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>F.D.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Máx. Dem. (W)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>I Dis. (A)</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Prot. ITM</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Prot. ID</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Conductor</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Ducto (ø)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>TD-01 (2º Piso)</t>
-        </is>
-      </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>Descripción de Carga</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Alumbrado General</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="I4" s="6">
-        <f>H4/(D4*0.9)</f>
-        <v/>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>2P-10A</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>No requiere</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>3x1.5 mm² LSOH</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>15 mm PVC-P</t>
+          <t>Pot. Instalada (W)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>F. Demanda</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Máx. Demanda (W)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>I. Diseño (A)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Conductor / Alimentador</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>ITM (A)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>ID (mA)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>TD-01 (2º Piso)</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Tomacorrientes Generales</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>220</v>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>2520</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>1764</v>
-      </c>
-      <c r="I5" s="10">
-        <f>H5/(D5*0.9)</f>
-        <v/>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>2P-16A</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>2P-25A-30mA</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>3x2.5 mm² LSOH</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>20 mm PVC-P</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Alumbrado General (Lámparas LED)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6">
+        <f>C5*D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="7">
+        <f>E5/(220*0.9)</f>
+        <v/>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>3 x 1.5 mm2 Cu - PVC 3/4"</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2P - 10A</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2P - 25A / 30mA</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>TD-01 (2º Piso)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Cocina (Pequeños Artefactos)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>960</v>
-      </c>
-      <c r="I6" s="6">
-        <f>H6/(D6*0.9)</f>
-        <v/>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>2P-20A</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>2P-25A-30mA</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>3x2.5 mm² LSOH</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>20 mm PVC-P</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Tomacorrientes Generales (TC)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>2520</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E6" s="10">
+        <f>C6*D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="11">
+        <f>E6/(220*0.9)</f>
+        <v/>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>3 x 2.5 mm2 Cu - PVC 3/4"</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>2P - 16A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>2P - 25A / 30mA</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>TD-02 (3º Piso)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Lavandería (Lavadora y Servicio)</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>220</v>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>360</v>
-      </c>
-      <c r="G7" s="10" t="n">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Tomacorrientes de Cocina</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D7" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="H7" s="9" t="n">
-        <v>288</v>
-      </c>
-      <c r="I7" s="10">
-        <f>H7/(D7*0.9)</f>
-        <v/>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>2P-16A</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>2P-25A-30mA</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>3x2.5 mm² LSOH</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>20 mm PVC-P</t>
+      <c r="E7" s="6">
+        <f>C7*D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="7">
+        <f>E7/(220*0.9)</f>
+        <v/>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>3 x 2.5 mm2 Cu - PVC 3/4"</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2P - 20A</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2P - 25A / 30mA</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>TD-02 (3º Piso)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Servicios Lavandería</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>360</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="10">
+        <f>C8*D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="11">
+        <f>E8/(220*0.9)</f>
+        <v/>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>3 x 2.5 mm2 Cu - PVC 3/4"</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>2P - 16A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>2P - 25A / 30mA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Carga Especial (Bomba de Agua)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>750</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="I8" s="6">
-        <f>H8/(D8*0.9)</f>
-        <v/>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>2P-16A</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>2P-25A-30mA</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>3x2.5 mm² LSOH</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>20 mm PVC-P</t>
+      <c r="E9" s="6">
+        <f>C9*D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="7">
+        <f>E9/(220*0.9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>3 x 2.5 mm2 Cu - PVC 3/4"</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2P - 16A</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>2P - 25A / 30mA</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL INSTALADO / MÁXIMA DEMANDA</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="13">
-        <f>SUM(F4:F8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="13">
-        <f>SUM(H4:H8)</f>
-        <v/>
-      </c>
-      <c r="I9" s="14">
-        <f>H9/(220*0.9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>ITM Gral: 2P-40A</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>ID Gral: 2P-40A-30mA</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>Acometida: 2x10mm² + 10mm²(T)</t>
-        </is>
-      </c>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>25 mm PVC-P</t>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>DEMANDA CONSOLIDADA</t>
+        </is>
+      </c>
+      <c r="C10" s="14">
+        <f>SUM(C5:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="15" t="inlineStr"/>
+      <c r="E10" s="14">
+        <f>SUM(E5:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="16">
+        <f>E10/(220*0.9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Acometida: 2 x 10 mm2 Cu + PE</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Gral: 2P-40A</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>ID: 2P-40A/30mA</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
